--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>111680296</v>
       </c>
       <c r="B3" t="n">
-        <v>90232</v>
+        <v>90242</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>111680296</v>
       </c>
       <c r="B3" t="n">
-        <v>90242</v>
+        <v>90254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>111680296</v>
       </c>
       <c r="B3" t="n">
-        <v>90254</v>
+        <v>90255</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>111680296</v>
       </c>
       <c r="B3" t="n">
-        <v>90255</v>
+        <v>90258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1485,6 +1485,815 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121525338</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>490900</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6948528</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121525314</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>490901</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6948530</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121525533</v>
+      </c>
+      <c r="B11" t="n">
+        <v>82391</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>490912</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6948557</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121525227</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90713</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>490891</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6948530</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Surdråg</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121525416</v>
+      </c>
+      <c r="B13" t="n">
+        <v>74713</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>490901</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6948540</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121525566</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>490938</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6948544</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121526317</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>490862</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6948449</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>111680296</v>
       </c>
       <c r="B3" t="n">
-        <v>90258</v>
+        <v>90264</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121525338</v>
+        <v>121525227</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490900</v>
+        <v>490891</v>
       </c>
       <c r="R9" t="n">
-        <v>6948528</v>
+        <v>6948530</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Surdråg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121525314</v>
+        <v>121525566</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,39 +1620,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490901</v>
+        <v>490938</v>
       </c>
       <c r="R10" t="n">
-        <v>6948530</v>
+        <v>6948544</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121525533</v>
+        <v>121525314</v>
       </c>
       <c r="B11" t="n">
-        <v>82391</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,34 +1732,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490912</v>
+        <v>490901</v>
       </c>
       <c r="R11" t="n">
-        <v>6948557</v>
+        <v>6948530</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121525227</v>
+        <v>121525338</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,21 +1849,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1868,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490891</v>
+        <v>490900</v>
       </c>
       <c r="R12" t="n">
-        <v>6948530</v>
+        <v>6948528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,12 +1918,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Surdråg</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,7 +1948,7 @@
         <v>121525416</v>
       </c>
       <c r="B13" t="n">
-        <v>74713</v>
+        <v>74714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121525566</v>
+        <v>121525533</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>82392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,21 +2073,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490938</v>
+        <v>490912</v>
       </c>
       <c r="R14" t="n">
-        <v>6948544</v>
+        <v>6948557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,7 +2172,7 @@
         <v>121526317</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -1490,7 +1490,7 @@
         <v>121525227</v>
       </c>
       <c r="B9" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121525566</v>
+        <v>121525533</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>82393</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490938</v>
+        <v>490912</v>
       </c>
       <c r="R10" t="n">
-        <v>6948544</v>
+        <v>6948557</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,7 +1719,7 @@
         <v>121525314</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121525338</v>
+        <v>121525566</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490900</v>
+        <v>490938</v>
       </c>
       <c r="R12" t="n">
-        <v>6948528</v>
+        <v>6948544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,10 +1945,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121525416</v>
+        <v>121526317</v>
       </c>
       <c r="B13" t="n">
-        <v>74714</v>
+        <v>57509</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1961,37 +1961,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490901</v>
+        <v>490862</v>
       </c>
       <c r="R13" t="n">
-        <v>6948540</v>
+        <v>6948449</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2020,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2040,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121525533</v>
+        <v>121525416</v>
       </c>
       <c r="B14" t="n">
-        <v>82392</v>
+        <v>74715</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,21 +2088,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2097,10 +2112,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490912</v>
+        <v>490901</v>
       </c>
       <c r="R14" t="n">
-        <v>6948557</v>
+        <v>6948540</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2147,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2157,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2184,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121526317</v>
+        <v>121525338</v>
       </c>
       <c r="B15" t="n">
-        <v>57508</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,47 +2200,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490862</v>
+        <v>490900</v>
       </c>
       <c r="R15" t="n">
-        <v>6948449</v>
+        <v>6948528</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2254,7 +2259,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,12 +2269,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121525227</v>
+        <v>121525314</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,31 +1503,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490891</v>
+        <v>490901</v>
       </c>
       <c r="R9" t="n">
         <v>6948530</v>
@@ -1562,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,12 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Surdråg</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121525314</v>
+        <v>121525338</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,39 +1732,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490901</v>
+        <v>490900</v>
       </c>
       <c r="R11" t="n">
-        <v>6948530</v>
+        <v>6948528</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1945,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121526317</v>
+        <v>121525416</v>
       </c>
       <c r="B13" t="n">
-        <v>57509</v>
+        <v>74715</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1961,47 +1956,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490862</v>
+        <v>490901</v>
       </c>
       <c r="R13" t="n">
-        <v>6948449</v>
+        <v>6948540</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2030,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,12 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121525416</v>
+        <v>121525227</v>
       </c>
       <c r="B14" t="n">
-        <v>74715</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,21 +2068,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2112,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490901</v>
+        <v>490891</v>
       </c>
       <c r="R14" t="n">
-        <v>6948540</v>
+        <v>6948530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2147,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2157,7 +2137,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Surdråg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121525338</v>
+        <v>121526317</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2200,37 +2185,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490900</v>
+        <v>490862</v>
       </c>
       <c r="R15" t="n">
-        <v>6948528</v>
+        <v>6948449</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2269,7 +2264,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121525533</v>
+        <v>121525338</v>
       </c>
       <c r="B10" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490912</v>
+        <v>490900</v>
       </c>
       <c r="R10" t="n">
-        <v>6948557</v>
+        <v>6948528</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121525338</v>
+        <v>121526317</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,37 +1732,47 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490900</v>
+        <v>490862</v>
       </c>
       <c r="R11" t="n">
-        <v>6948528</v>
+        <v>6948449</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1791,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1811,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121525566</v>
+        <v>121525416</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,21 +1859,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1868,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490938</v>
+        <v>490901</v>
       </c>
       <c r="R12" t="n">
-        <v>6948544</v>
+        <v>6948540</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121525416</v>
+        <v>121525227</v>
       </c>
       <c r="B13" t="n">
-        <v>74715</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1971,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1980,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490901</v>
+        <v>490891</v>
       </c>
       <c r="R13" t="n">
-        <v>6948540</v>
+        <v>6948530</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2040,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Surdråg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121525227</v>
+        <v>121525533</v>
       </c>
       <c r="B14" t="n">
-        <v>90720</v>
+        <v>82393</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,21 +2088,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2112,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490891</v>
+        <v>490912</v>
       </c>
       <c r="R14" t="n">
-        <v>6948530</v>
+        <v>6948557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,7 +2147,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,12 +2157,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Surdråg</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2184,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121526317</v>
+        <v>121525566</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,47 +2200,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490862</v>
+        <v>490938</v>
       </c>
       <c r="R15" t="n">
-        <v>6948449</v>
+        <v>6948544</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2254,7 +2259,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,12 +2269,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121525314</v>
+        <v>121526317</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,27 +1503,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1532,13 +1537,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490901</v>
+        <v>490862</v>
       </c>
       <c r="R9" t="n">
-        <v>6948530</v>
+        <v>6948449</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1582,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121525338</v>
+        <v>121525314</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,34 +1630,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490900</v>
+        <v>490901</v>
       </c>
       <c r="R10" t="n">
-        <v>6948528</v>
+        <v>6948530</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1704,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121526317</v>
+        <v>121525227</v>
       </c>
       <c r="B11" t="n">
-        <v>57509</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,47 +1747,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490862</v>
+        <v>490891</v>
       </c>
       <c r="R11" t="n">
-        <v>6948449</v>
+        <v>6948530</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1801,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1811,12 +1816,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sång och observerad fågel</t>
+          <t>Surdråg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121525416</v>
+        <v>121525338</v>
       </c>
       <c r="B12" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,21 +1864,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490901</v>
+        <v>490900</v>
       </c>
       <c r="R12" t="n">
-        <v>6948540</v>
+        <v>6948528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1923,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1933,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,10 +1960,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121525227</v>
+        <v>121525416</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>74715</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,21 +1976,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1995,10 +2000,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490891</v>
+        <v>490901</v>
       </c>
       <c r="R13" t="n">
-        <v>6948530</v>
+        <v>6948540</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2035,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,12 +2045,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Surdråg</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121525533</v>
+        <v>121525566</v>
       </c>
       <c r="B14" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,21 +2088,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490912</v>
+        <v>490938</v>
       </c>
       <c r="R14" t="n">
-        <v>6948557</v>
+        <v>6948544</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,10 +2184,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121525566</v>
+        <v>121525533</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490938</v>
+        <v>490912</v>
       </c>
       <c r="R15" t="n">
-        <v>6948544</v>
+        <v>6948557</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2294,6 +2294,224 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121672040</v>
+      </c>
+      <c r="B16" t="n">
+        <v>88044</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>510</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>490914</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6948596</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121669592</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78614</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>490858</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6948475</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -1490,7 +1490,7 @@
         <v>121526317</v>
       </c>
       <c r="B9" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>121525314</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121525227</v>
+        <v>121525566</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1747,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490891</v>
+        <v>490938</v>
       </c>
       <c r="R11" t="n">
-        <v>6948530</v>
+        <v>6948544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,12 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Surdråg</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,7 +1846,7 @@
         <v>121525338</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1963,7 +1958,7 @@
         <v>121525416</v>
       </c>
       <c r="B13" t="n">
-        <v>74715</v>
+        <v>74722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2072,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121525566</v>
+        <v>121525227</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,21 +2083,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2112,10 +2107,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490938</v>
+        <v>490891</v>
       </c>
       <c r="R14" t="n">
-        <v>6948544</v>
+        <v>6948530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2147,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2157,7 +2152,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Surdråg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,7 +2187,7 @@
         <v>121525533</v>
       </c>
       <c r="B15" t="n">
-        <v>82393</v>
+        <v>82400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>121672040</v>
       </c>
       <c r="B16" t="n">
-        <v>88044</v>
+        <v>88046</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>121669592</v>
       </c>
       <c r="B17" t="n">
-        <v>78614</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121525338</v>
+        <v>121525416</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490900</v>
+        <v>490901</v>
       </c>
       <c r="R9" t="n">
-        <v>6948528</v>
+        <v>6948540</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121525416</v>
+        <v>121525533</v>
       </c>
       <c r="B10" t="n">
-        <v>74722</v>
+        <v>82400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,21 +1615,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490901</v>
+        <v>490912</v>
       </c>
       <c r="R10" t="n">
-        <v>6948540</v>
+        <v>6948557</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121525533</v>
+        <v>121525227</v>
       </c>
       <c r="B11" t="n">
-        <v>82400</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490912</v>
+        <v>490891</v>
       </c>
       <c r="R11" t="n">
-        <v>6948557</v>
+        <v>6948530</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Surdråg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121525566</v>
+        <v>121526317</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,37 +1844,47 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490938</v>
+        <v>490862</v>
       </c>
       <c r="R12" t="n">
-        <v>6948544</v>
+        <v>6948449</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1923,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121526317</v>
+        <v>121525566</v>
       </c>
       <c r="B13" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,47 +1971,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490862</v>
+        <v>490938</v>
       </c>
       <c r="R13" t="n">
-        <v>6948449</v>
+        <v>6948544</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2020,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,12 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121525227</v>
+        <v>121525314</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,31 +2083,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490891</v>
+        <v>490901</v>
       </c>
       <c r="R14" t="n">
         <v>6948530</v>
@@ -2137,7 +2147,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,12 +2157,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Surdråg</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,10 +2184,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121525314</v>
+        <v>121525338</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,39 +2200,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490901</v>
+        <v>490900</v>
       </c>
       <c r="R15" t="n">
-        <v>6948530</v>
+        <v>6948528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2512,6 +2512,459 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121824033</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57510</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>490893</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6948570</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121820599</v>
+      </c>
+      <c r="B19" t="n">
+        <v>82400</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>490952</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6948547</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121821682</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>491074</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6948700</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121820616</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74722</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>490952</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6948552</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121525416</v>
+        <v>121526317</v>
       </c>
       <c r="B9" t="n">
-        <v>74722</v>
+        <v>57510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,37 +1503,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490901</v>
+        <v>490862</v>
       </c>
       <c r="R9" t="n">
-        <v>6948540</v>
+        <v>6948449</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1582,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121525533</v>
+        <v>121525416</v>
       </c>
       <c r="B10" t="n">
-        <v>82400</v>
+        <v>74722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,21 +1630,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1639,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490912</v>
+        <v>490901</v>
       </c>
       <c r="R10" t="n">
-        <v>6948557</v>
+        <v>6948540</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1699,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121525227</v>
+        <v>121525566</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,21 +1742,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490891</v>
+        <v>490938</v>
       </c>
       <c r="R11" t="n">
-        <v>6948530</v>
+        <v>6948544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,12 +1811,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Surdråg</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121526317</v>
+        <v>121525227</v>
       </c>
       <c r="B12" t="n">
-        <v>57510</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,47 +1854,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490862</v>
+        <v>490891</v>
       </c>
       <c r="R12" t="n">
-        <v>6948449</v>
+        <v>6948530</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Sång och observerad fågel</t>
+          <t>Surdråg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,7 +1955,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121525566</v>
+        <v>121525338</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490938</v>
+        <v>490900</v>
       </c>
       <c r="R13" t="n">
-        <v>6948544</v>
+        <v>6948528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121525314</v>
+        <v>121525533</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,39 +2083,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490901</v>
+        <v>490912</v>
       </c>
       <c r="R14" t="n">
-        <v>6948530</v>
+        <v>6948557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2147,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2157,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121525338</v>
+        <v>121525314</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2200,34 +2195,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490900</v>
+        <v>490901</v>
       </c>
       <c r="R15" t="n">
-        <v>6948528</v>
+        <v>6948530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,10 +2296,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121669592</v>
+        <v>121672040</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>88046</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,37 +2312,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sågbacken, Sågbacken, Jmt</t>
+          <t>Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490858</v>
+        <v>490914</v>
       </c>
       <c r="R16" t="n">
-        <v>6948475</v>
+        <v>6948596</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,27 +2372,18 @@
           <t>2024-12-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-19</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121672040</v>
+        <v>121669592</v>
       </c>
       <c r="B17" t="n">
-        <v>88046</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,40 +2418,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sågbacken, Jmt</t>
+          <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490914</v>
+        <v>490858</v>
       </c>
       <c r="R17" t="n">
-        <v>6948596</v>
+        <v>6948475</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2484,18 +2475,27 @@
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121824033</v>
+        <v>121820616</v>
       </c>
       <c r="B18" t="n">
-        <v>57510</v>
+        <v>74722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,39 +2530,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490893</v>
+        <v>490952</v>
       </c>
       <c r="R18" t="n">
-        <v>6948570</v>
+        <v>6948552</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121820599</v>
+        <v>121821682</v>
       </c>
       <c r="B19" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,21 +2642,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2671,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490952</v>
+        <v>491074</v>
       </c>
       <c r="R19" t="n">
-        <v>6948547</v>
+        <v>6948700</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121821682</v>
+        <v>121824033</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,34 +2754,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491074</v>
+        <v>490893</v>
       </c>
       <c r="R20" t="n">
-        <v>6948700</v>
+        <v>6948570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,10 +2855,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121820616</v>
+        <v>121820599</v>
       </c>
       <c r="B21" t="n">
-        <v>74722</v>
+        <v>82400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2871,21 +2871,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,7 +2898,7 @@
         <v>490952</v>
       </c>
       <c r="R21" t="n">
-        <v>6948552</v>
+        <v>6948547</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -2514,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121821682</v>
+        <v>121820616</v>
       </c>
       <c r="B18" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,21 +2530,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491074</v>
+        <v>490952</v>
       </c>
       <c r="R18" t="n">
-        <v>6948700</v>
+        <v>6948552</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121820599</v>
+        <v>121821682</v>
       </c>
       <c r="B19" t="n">
-        <v>82432</v>
+        <v>78645</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,21 +2642,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490952</v>
+        <v>491074</v>
       </c>
       <c r="R19" t="n">
-        <v>6948547</v>
+        <v>6948700</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121820616</v>
+        <v>121824033</v>
       </c>
       <c r="B20" t="n">
-        <v>74747</v>
+        <v>57527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,34 +2754,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490952</v>
+        <v>490893</v>
       </c>
       <c r="R20" t="n">
-        <v>6948552</v>
+        <v>6948570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2813,7 +2818,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,7 +2828,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,10 +2855,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121824033</v>
+        <v>121820599</v>
       </c>
       <c r="B21" t="n">
-        <v>57527</v>
+        <v>82432</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2866,39 +2871,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490893</v>
+        <v>490952</v>
       </c>
       <c r="R21" t="n">
-        <v>6948570</v>
+        <v>6948547</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2965,6 +2965,118 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126101542</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>490892</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6948416</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -2970,7 +2970,7 @@
         <v>126101542</v>
       </c>
       <c r="B22" t="n">
-        <v>58079</v>
+        <v>58080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -2970,7 +2970,7 @@
         <v>126101542</v>
       </c>
       <c r="B22" t="n">
-        <v>58080</v>
+        <v>58084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -2970,7 +2970,7 @@
         <v>126101542</v>
       </c>
       <c r="B22" t="n">
-        <v>58084</v>
+        <v>58087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,122 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130243107</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98833</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>490904</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6948580</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -3082,7 +3082,7 @@
         <v>130243107</v>
       </c>
       <c r="B23" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -3082,7 +3082,7 @@
         <v>130243107</v>
       </c>
       <c r="B23" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -3082,7 +3082,7 @@
         <v>130243107</v>
       </c>
       <c r="B23" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -3082,7 +3082,7 @@
         <v>130243107</v>
       </c>
       <c r="B23" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -3082,7 +3082,7 @@
         <v>130243107</v>
       </c>
       <c r="B23" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -3082,7 +3082,7 @@
         <v>130243107</v>
       </c>
       <c r="B23" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -3082,7 +3082,7 @@
         <v>130243107</v>
       </c>
       <c r="B23" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111680533</v>
+        <v>120088522</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sågbacken (Sågbacken), Jmt</t>
+          <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490860</v>
+        <v>490858</v>
       </c>
       <c r="R2" t="n">
-        <v>6948446</v>
+        <v>6948582</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111680296</v>
+        <v>121672040</v>
       </c>
       <c r="B3" t="n">
-        <v>90264</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5754</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,17 +816,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sågbacken, Sågbacken, Jmt</t>
+          <t>Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490869</v>
+        <v>490914</v>
       </c>
       <c r="R3" t="n">
-        <v>6948441</v>
+        <v>6948596</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,59 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117571885</v>
+        <v>121525227</v>
       </c>
       <c r="B4" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sågbacken (Sågbacken), Jmt</t>
+          <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490924</v>
+        <v>490891</v>
       </c>
       <c r="R4" t="n">
-        <v>6948557</v>
+        <v>6948530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,22 +948,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Surdråg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,50 +995,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117575488</v>
+        <v>121525533</v>
       </c>
       <c r="B5" t="n">
-        <v>90466</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sågbacken (Sågbacken), Jmt</t>
+          <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490905</v>
+        <v>490912</v>
       </c>
       <c r="R5" t="n">
-        <v>6948530</v>
+        <v>6948557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,27 +1060,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vid hänsynskrävande surdråg</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,50 +1102,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117574427</v>
+        <v>121820599</v>
       </c>
       <c r="B6" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sågbacken (Sågbacken), Jmt</t>
+          <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490950</v>
+        <v>490952</v>
       </c>
       <c r="R6" t="n">
-        <v>6948608</v>
+        <v>6948547</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,22 +1167,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,12 +1212,7 @@
         <v>117572068</v>
       </c>
       <c r="B7" t="n">
-        <v>90466</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1240,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sågbacken (Sågbacken), Jmt</t>
+          <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1366,53 +1316,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117570068</v>
+        <v>117575488</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sågbacken (Sågbacken), Jmt</t>
+          <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490875</v>
+        <v>490905</v>
       </c>
       <c r="R8" t="n">
-        <v>6948553</v>
+        <v>6948530</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,12 +1396,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Nära hänsynskrävande surdråg</t>
+          <t>Vid hänsynskrävande surdråg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,7 +1410,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1487,15 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121525227</v>
+        <v>111680296</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,37 +1439,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5754</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490891</v>
+        <v>490869</v>
       </c>
       <c r="R9" t="n">
-        <v>6948530</v>
+        <v>6948441</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,27 +1496,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Surdråg</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,6 +1520,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1604,63 +1539,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121526317</v>
+        <v>117570068</v>
       </c>
       <c r="B10" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490862</v>
+        <v>490875</v>
       </c>
       <c r="R10" t="n">
-        <v>6948449</v>
+        <v>6948553</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,27 +1607,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sång och observerad fågel</t>
+          <t>Nära hänsynskrävande surdråg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,6 +1636,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1731,19 +1655,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121525566</v>
+        <v>117574285</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1771,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490938</v>
+        <v>490921</v>
       </c>
       <c r="R11" t="n">
-        <v>6948544</v>
+        <v>6948632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,22 +1720,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,37 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121525416</v>
+        <v>120086700</v>
       </c>
       <c r="B12" t="n">
-        <v>74722</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490901</v>
+        <v>490840</v>
       </c>
       <c r="R12" t="n">
-        <v>6948540</v>
+        <v>6948476</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,22 +1827,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,37 +1869,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121525533</v>
+        <v>121525338</v>
       </c>
       <c r="B13" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1995,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490912</v>
+        <v>490900</v>
       </c>
       <c r="R13" t="n">
-        <v>6948557</v>
+        <v>6948528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +1939,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +1949,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,55 +1976,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121525314</v>
+        <v>121525566</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490901</v>
+        <v>490938</v>
       </c>
       <c r="R14" t="n">
-        <v>6948530</v>
+        <v>6948544</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2147,7 +2046,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2157,7 +2056,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,19 +2083,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121525338</v>
+        <v>121525795</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2224,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490900</v>
+        <v>490927</v>
       </c>
       <c r="R15" t="n">
-        <v>6948528</v>
+        <v>6948615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2259,7 +2153,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2269,7 +2163,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,56 +2190,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121672040</v>
+        <v>121669592</v>
       </c>
       <c r="B16" t="n">
-        <v>88063</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sågbacken, Jmt</t>
+          <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490914</v>
+        <v>490858</v>
       </c>
       <c r="R16" t="n">
-        <v>6948596</v>
+        <v>6948475</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2372,18 +2258,27 @@
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2402,19 +2297,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121669592</v>
+        <v>121821682</v>
       </c>
       <c r="B17" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2442,10 +2332,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490858</v>
+        <v>491074</v>
       </c>
       <c r="R17" t="n">
-        <v>6948475</v>
+        <v>6948700</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,22 +2362,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,15 +2404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121820616</v>
+        <v>121525416</v>
       </c>
       <c r="B18" t="n">
-        <v>74747</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,10 +2439,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490952</v>
+        <v>490901</v>
       </c>
       <c r="R18" t="n">
-        <v>6948552</v>
+        <v>6948540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,22 +2469,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,15 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121821682</v>
+        <v>121820616</v>
       </c>
       <c r="B19" t="n">
-        <v>78645</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,21 +2522,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491074</v>
+        <v>490952</v>
       </c>
       <c r="R19" t="n">
-        <v>6948700</v>
+        <v>6948552</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2701,7 +2581,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2591,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,55 +2618,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121824033</v>
+        <v>121838169</v>
       </c>
       <c r="B20" t="n">
-        <v>57527</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sågbacken, Sågbacken, Jmt</t>
+          <t>Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490893</v>
+        <v>490947</v>
       </c>
       <c r="R20" t="n">
-        <v>6948570</v>
+        <v>6948632</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2816,19 +2694,9 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,50 +2723,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121820599</v>
+        <v>126616802</v>
       </c>
       <c r="B21" t="n">
-        <v>82432</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490952</v>
+        <v>490870</v>
       </c>
       <c r="R21" t="n">
-        <v>6948547</v>
+        <v>6948578</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2925,22 +2793,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2967,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126101542</v>
+        <v>121525314</v>
       </c>
       <c r="B22" t="n">
-        <v>58087</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2978,27 +2846,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3007,13 +2875,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490892</v>
+        <v>490901</v>
       </c>
       <c r="R22" t="n">
-        <v>6948416</v>
+        <v>6948530</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3037,22 +2905,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,42 +2947,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130243107</v>
+        <v>121822772</v>
       </c>
       <c r="B23" t="n">
-        <v>98957</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3123,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490904</v>
+        <v>490948</v>
       </c>
       <c r="R23" t="n">
-        <v>6948580</v>
+        <v>6948639</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3153,22 +3017,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,6 +3056,1587 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126883092</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490885</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6948590</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126101542</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>490892</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6948416</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121526317</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>490862</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6948449</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121824033</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>490893</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6948570</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>111680533</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>490860</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6948446</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>117491664</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>490869</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6948548</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Nära hänsynskrävande surdråg</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>117492216</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>490857</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6948517</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>117571698</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>490924</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6948557</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>117574427</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>490950</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6948608</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>117575343</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>490840</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6948518</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>117575821</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>490837</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6948462</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126882900</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>490860</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6948583</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130243107</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sågbacken, Sågbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>490904</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6948580</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127505207</v>
+      </c>
+      <c r="B37" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Siljebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>491178</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6948135</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,38 +3171,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126101542</v>
+        <v>134692928</v>
       </c>
       <c r="B25" t="n">
-        <v>58388</v>
+        <v>57153</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103001</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3211,13 +3210,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490892</v>
+        <v>491009</v>
       </c>
       <c r="R25" t="n">
-        <v>6948416</v>
+        <v>6948318</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3241,22 +3240,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>En kull med järpkycklingar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,22 +3275,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121526317</v>
+        <v>126101542</v>
       </c>
       <c r="B26" t="n">
-        <v>58114</v>
+        <v>58388</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,32 +3298,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3328,13 +3327,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490862</v>
+        <v>490892</v>
       </c>
       <c r="R26" t="n">
-        <v>6948449</v>
+        <v>6948416</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3358,27 +3357,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3405,7 +3399,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121824033</v>
+        <v>121526317</v>
       </c>
       <c r="B27" t="n">
         <v>58114</v>
@@ -3434,9 +3428,14 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3445,13 +3444,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490893</v>
+        <v>490862</v>
       </c>
       <c r="R27" t="n">
-        <v>6948570</v>
+        <v>6948449</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3475,22 +3474,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3517,49 +3521,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111680533</v>
+        <v>121824033</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490860</v>
+        <v>490893</v>
       </c>
       <c r="R28" t="n">
-        <v>6948446</v>
+        <v>6948570</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3583,22 +3591,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,7 +3633,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117491664</v>
+        <v>111680533</v>
       </c>
       <c r="B29" t="n">
         <v>99118</v>
@@ -3653,32 +3661,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490869</v>
+        <v>490860</v>
       </c>
       <c r="R29" t="n">
-        <v>6948548</v>
+        <v>6948446</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3702,27 +3699,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Nära hänsynskrävande surdråg</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3731,7 +3723,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3750,7 +3741,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117492216</v>
+        <v>117491664</v>
       </c>
       <c r="B30" t="n">
         <v>99118</v>
@@ -3780,7 +3771,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3788,16 +3779,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490857</v>
+        <v>490869</v>
       </c>
       <c r="R30" t="n">
-        <v>6948517</v>
+        <v>6948548</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3829,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3839,7 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Nära hänsynskrävande surdråg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,6 +3847,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3866,7 +3866,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117571698</v>
+        <v>117492216</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490924</v>
+        <v>490857</v>
       </c>
       <c r="R31" t="n">
-        <v>6948557</v>
+        <v>6948517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,22 +3940,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3982,7 +3982,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117574427</v>
+        <v>117571698</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -4010,17 +4010,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490950</v>
+        <v>490924</v>
       </c>
       <c r="R32" t="n">
-        <v>6948608</v>
+        <v>6948557</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,7 +4061,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4062,7 +4071,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4089,7 +4098,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117575343</v>
+        <v>117574427</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4124,10 +4133,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490840</v>
+        <v>490950</v>
       </c>
       <c r="R33" t="n">
-        <v>6948518</v>
+        <v>6948608</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,7 +4168,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4169,7 +4178,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4196,7 +4205,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117575821</v>
+        <v>117575343</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4231,10 +4240,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490837</v>
+        <v>490840</v>
       </c>
       <c r="R34" t="n">
-        <v>6948462</v>
+        <v>6948518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4266,7 +4275,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4276,7 +4285,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,7 +4312,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126882900</v>
+        <v>117575821</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4331,26 +4340,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490860</v>
+        <v>490837</v>
       </c>
       <c r="R35" t="n">
-        <v>6948583</v>
+        <v>6948462</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4377,22 +4377,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4419,7 +4419,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130243107</v>
+        <v>126882900</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4463,10 +4463,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490904</v>
+        <v>490860</v>
       </c>
       <c r="R36" t="n">
-        <v>6948580</v>
+        <v>6948583</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4493,22 +4493,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4535,52 +4535,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127505207</v>
+        <v>130243107</v>
       </c>
       <c r="B37" t="n">
-        <v>102464</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221343</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Siljebodarna, Jmt</t>
+          <t>Sågbacken, Sågbacken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491178</v>
+        <v>490904</v>
       </c>
       <c r="R37" t="n">
-        <v>6948135</v>
+        <v>6948580</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4604,12 +4609,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4624,15 +4639,116 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127505207</v>
+      </c>
+      <c r="B38" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Siljebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>491178</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6948135</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Staffan Fridh</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>Vigge Ulfsson</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 53455-2024 artfynd.xlsx
+++ b/artfynd/A 53455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088522</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672040</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121525227</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121525533</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121820599</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117572068</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117575488</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111680296</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117570068</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117574285</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1866,6 +1921,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086700</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,6 +2033,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121525338</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2080,6 +2145,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121525566</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2187,6 +2257,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121525795</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2294,6 +2369,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669592</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2401,6 +2481,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121821682</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2508,6 +2593,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121525416</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2615,6 +2705,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121820616</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2720,6 +2815,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121838169</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2832,6 +2932,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126616802</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2944,6 +3049,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121525314</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3056,6 +3166,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121822772</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3168,6 +3283,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126883092</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3284,6 +3404,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134692928</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3396,6 +3521,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126101542</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3518,6 +3648,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121526317</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3630,6 +3765,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121824033</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3738,6 +3878,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111680533</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3863,6 +4008,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117491664</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3979,6 +4129,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492216</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4095,6 +4250,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117571698</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4202,6 +4362,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117574427</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4309,6 +4474,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117575343</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4416,6 +4586,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117575821</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4532,6 +4707,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126882900</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4648,6 +4828,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130243107</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4753,8 +4938,52 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127505207</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>